--- a/public/inputs/y12-spanish-a-level - input.xlsx
+++ b/public/inputs/y12-spanish-a-level - input.xlsx
@@ -441,10 +441,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unidad 0 · Understanding SpanishA Level 9844</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Unidad 0 · Understanding Spanish A Level 9844</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +456,6 @@
           <t>Unidad 1 · From B1 to B2/C1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,7 +468,6 @@
           <t>Unidad 2 · Advanced vocabulary and expression</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,7 +480,6 @@
           <t>Unidad 3 · Grammar for sophisticated</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,7 +492,6 @@
           <t>Unidad 4 · Critical thinking in Spanish</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,7 +504,6 @@
           <t>Unidad 5 · Reading at B2–C1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,7 +516,6 @@
           <t>Unidad 6 · Explicit and implicit meaning</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,7 +528,6 @@
           <t>Unidad 7 · Attitudes, emotions and opinions</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,7 +540,6 @@
           <t>Unidad 8 · Argument, evidence and conclusions</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>Unidad 9 · Vocabulary in context</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,7 +564,6 @@
           <t>Unidad 10 · Comparing thematically linked texts</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,7 +576,6 @@
           <t>Unidad 11 · Grammar through reading</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -600,7 +588,6 @@
           <t>Unidad 12 · Paper 1 examination strategy</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,7 +600,6 @@
           <t>Unidad 13 · Paper 1 practice</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -626,7 +612,6 @@
           <t>Unidad 14 · Writing at B2–C1</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -639,7 +624,6 @@
           <t>Unidad 15 · Argumentative writing</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -652,7 +636,6 @@
           <t>Unidad 16 · Discursive writing</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -665,7 +648,6 @@
           <t>Unidad 17 · Descriptive writing</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -678,7 +660,6 @@
           <t>Unidad 18 · Narrative writing</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -691,7 +672,6 @@
           <t>Unidad 19 · Organisation and cohesion</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -704,7 +684,6 @@
           <t>Unidad 20 · Accuracy and linguistic range</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -717,7 +696,6 @@
           <t>Unidad 21 · Paper 2 examination strategy</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -730,7 +708,6 @@
           <t>Unidad 22 · Culture</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -743,7 +720,6 @@
           <t>Unidad 23 · Health and well-being</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -756,7 +732,6 @@
           <t>Unidad 24 · Education and future plans</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -769,7 +744,6 @@
           <t>Unidad 25 · Community and society</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -782,7 +756,6 @@
           <t>Unidad 26 · Our responsibility for the planet</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -795,7 +768,6 @@
           <t>Unidad 27 · Science and technology</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -805,10 +777,9 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Unidad 28 · How to study literature atA Level</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Unidad 28 · How to study literature at A Level</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -821,7 +792,6 @@
           <t>Unidad 29 · Literary analysis toolkit</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -831,10 +801,9 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unidad 30 · SectionA · La casa de Bernarda Alba</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Unidad 30 · Section A · La casa de Bernarda Alba</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -844,10 +813,9 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unidad 31 · SectionA · Eva Luna</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Unidad 31 · Section A · Eva Luna</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -857,10 +825,9 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unidad 32 · SectionA · La sombra del viento</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Unidad 32 · Section A · La sombra del viento</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -873,7 +840,6 @@
           <t>Unidad 33 · Mastering the passage-based</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -883,10 +849,9 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Unidad 34 · SectionB · Crónica de una muerte</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Unidad 34 · Section B · Crónica de una muerte</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -896,10 +861,9 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Unidad 35 · SectionB · Las bicicletas son para el</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Unidad 35 · Section B · Las bicicletas son para el</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -909,10 +873,9 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Unidad 36 · SectionB · Como agua para</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Unidad 36 · Section B · Como agua para</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -925,7 +888,6 @@
           <t>Unidad 37 · Mastering the literature essay</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -938,7 +900,6 @@
           <t>Unidad 38 · Think like an examiner</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -951,7 +912,6 @@
           <t>Unidad 39 · Time management</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
